--- a/data_lake/industry/CFM/uMCP.xlsx
+++ b/data_lake/industry/CFM/uMCP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EB12B1-7E7D-4741-98A2-EDB0D3F964B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286BA6F1-B446-4152-8DEA-B8C3A19AEB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,31 +70,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -103,9 +103,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,50 +132,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -453,19 +458,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -511,7 +516,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -534,7 +539,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -557,7 +562,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -580,7 +585,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -603,7 +608,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -626,7 +631,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -649,7 +654,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -672,7 +677,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -695,7 +700,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -718,7 +723,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -741,7 +746,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -764,7 +769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -787,7 +792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -810,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -833,7 +838,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -856,7 +861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -879,7 +884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -902,7 +907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -925,7 +930,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -948,7 +953,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -971,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -994,7 +999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1017,7 +1022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1040,7 +1045,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1063,7 +1068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1086,7 +1091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1109,7 +1114,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1132,7 +1137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1155,7 +1160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1178,7 +1183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1201,7 +1206,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1224,7 +1229,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1247,7 +1252,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1270,7 +1275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1293,7 +1298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1316,7 +1321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1339,7 +1344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1362,7 +1367,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1385,7 +1390,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1408,7 +1413,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1431,7 +1436,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1454,7 +1459,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1477,7 +1482,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1500,7 +1505,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1523,7 +1528,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1546,7 +1551,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1566,6 +1571,121 @@
         <v>92.2</v>
       </c>
       <c r="G48" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F49" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G49" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F50" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G50" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F51" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G51" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F52" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G52" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F53" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G53" s="9">
         <v>91</v>
       </c>
     </row>
@@ -1577,19 +1697,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1635,7 +1755,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1658,7 +1778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1681,7 +1801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1704,7 +1824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1727,7 +1847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1750,7 +1870,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1773,7 +1893,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1796,7 +1916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1819,7 +1939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1842,7 +1962,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1865,7 +1985,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1888,7 +2008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1911,7 +2031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1934,7 +2054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1957,7 +2077,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1980,7 +2100,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2003,7 +2123,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2026,7 +2146,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2049,7 +2169,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2072,7 +2192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2095,7 +2215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2118,7 +2238,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2141,7 +2261,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2164,7 +2284,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2187,7 +2307,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2210,7 +2330,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2233,7 +2353,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2256,7 +2376,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2279,7 +2399,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2302,7 +2422,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2325,7 +2445,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2348,7 +2468,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2371,7 +2491,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2394,7 +2514,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2417,7 +2537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2440,7 +2560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2463,7 +2583,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2486,7 +2606,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2509,7 +2629,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2532,7 +2652,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2555,7 +2675,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2578,7 +2698,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2601,7 +2721,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2624,7 +2744,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2647,7 +2767,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2670,7 +2790,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2690,6 +2810,121 @@
         <v>110</v>
       </c>
       <c r="G48" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F49" s="12">
+        <v>110</v>
+      </c>
+      <c r="G49" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F50" s="12">
+        <v>110</v>
+      </c>
+      <c r="G50" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F51" s="12">
+        <v>110</v>
+      </c>
+      <c r="G51" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F52" s="12">
+        <v>110</v>
+      </c>
+      <c r="G52" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F53" s="12">
+        <v>110</v>
+      </c>
+      <c r="G53" s="12">
         <v>109</v>
       </c>
     </row>
@@ -2701,19 +2936,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2736,7 +2971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2759,7 +2994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2782,7 +3017,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2805,7 +3040,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2828,7 +3063,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2851,7 +3086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2874,7 +3109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2897,7 +3132,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2920,7 +3155,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2943,7 +3178,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2966,7 +3201,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2989,7 +3224,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3012,7 +3247,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3035,7 +3270,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3058,7 +3293,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3081,7 +3316,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3104,7 +3339,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3127,7 +3362,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3150,7 +3385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3173,7 +3408,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3196,7 +3431,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3219,7 +3454,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3242,7 +3477,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3265,7 +3500,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3288,7 +3523,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3311,7 +3546,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3334,7 +3569,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3357,7 +3592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3380,7 +3615,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3403,7 +3638,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3426,7 +3661,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3449,7 +3684,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3472,7 +3707,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3495,7 +3730,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3518,7 +3753,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3541,7 +3776,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3564,7 +3799,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3587,7 +3822,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3610,7 +3845,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3633,7 +3868,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3656,7 +3891,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3679,7 +3914,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3702,7 +3937,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3725,7 +3960,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3748,7 +3983,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3771,7 +4006,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3794,7 +4029,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3814,6 +4049,121 @@
         <v>137</v>
       </c>
       <c r="G48" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>131</v>
+      </c>
+      <c r="F49" s="14">
+        <v>137</v>
+      </c>
+      <c r="G49" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>131</v>
+      </c>
+      <c r="F50" s="14">
+        <v>137</v>
+      </c>
+      <c r="G50" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>131</v>
+      </c>
+      <c r="F51" s="14">
+        <v>137</v>
+      </c>
+      <c r="G51" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>131</v>
+      </c>
+      <c r="F52" s="14">
+        <v>137</v>
+      </c>
+      <c r="G52" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>131</v>
+      </c>
+      <c r="F53" s="14">
+        <v>137</v>
+      </c>
+      <c r="G53" s="14">
         <v>134</v>
       </c>
     </row>
@@ -3825,21 +4175,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="14"/>
-    <col min="6" max="6" width="9.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="15"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3862,7 +4212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3885,7 +4235,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3908,7 +4258,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3931,7 +4281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3954,7 +4304,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3977,7 +4327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4000,7 +4350,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4023,7 +4373,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4046,7 +4396,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4069,7 +4419,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4092,7 +4442,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4115,7 +4465,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4138,7 +4488,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4161,7 +4511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4184,7 +4534,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4207,7 +4557,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4230,7 +4580,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4253,7 +4603,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4276,7 +4626,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4299,7 +4649,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4322,7 +4672,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4345,7 +4695,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4368,7 +4718,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4391,7 +4741,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4414,7 +4764,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4437,7 +4787,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4460,7 +4810,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4483,7 +4833,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4506,7 +4856,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4529,7 +4879,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4552,7 +4902,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4575,7 +4925,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4598,7 +4948,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4621,7 +4971,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4644,7 +4994,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4667,7 +5017,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4690,7 +5040,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4713,7 +5063,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4736,7 +5086,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -4759,7 +5109,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -4782,7 +5132,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -4805,7 +5155,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -4828,7 +5178,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -4851,7 +5201,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -4874,7 +5224,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4897,7 +5247,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4920,7 +5270,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4940,6 +5290,121 @@
         <v>163.5</v>
       </c>
       <c r="G48" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>160</v>
+      </c>
+      <c r="F49" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G49" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>160</v>
+      </c>
+      <c r="F50" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G50" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>160</v>
+      </c>
+      <c r="F51" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G51" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>160</v>
+      </c>
+      <c r="F52" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G52" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>160</v>
+      </c>
+      <c r="F53" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G53" s="14">
         <v>161</v>
       </c>
     </row>
